--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y274"/>
+  <dimension ref="A1:Y309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.5.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: A large assortment of Faney Embroidered Hose, in Cotton, Lisle, Cashmere and sÄ±k;</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: COâ€™S.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L28: isolated marker/symbol line :: e</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -685,25 +689,17 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>803</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>L446: possible duplicated/overlap line with previous line (similarity 63%) :: South Brant ï¼› Mr. Balfour over 800 in</t>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | possible duplicated/overlap line with previous line (similarity 64%) :: South Brant ； Mr. Balfour over 800 in</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>L437: candidate OCR token mismatch vs other OCR: "presen" vs "present" :: tion will have to be held in the presen</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "85c Saltfleet 1" :: â€”____________________=85c. â€” â€”________________</t>
-        </is>
-      </c>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr">
         <is>
           <t>L158: suspicious token(s): 2Bc (letter/digit mix) :: EXTRA VALUE in Ribbed Cotton Vests, half sleeves, 2 for 2Bc.</t>
@@ -711,24 +707,24 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L50: suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c each—Perfect Goods.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L199: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF06 FULLWIDTH AMPERSAND | isolated marker/symbol line :: ＆</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: S</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -789,16 +785,8 @@
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>L443: candidate OCR token mismatch vs other OCR: "shawn" vs "shown" :: large Liberal majorities are shawn. Mr.</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>L576: suspicious token(s): canidaton25 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "holidays" vs "Come nd canidaton25 better matched out after" :: the Come nd canidaton25</t>
-        </is>
-      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
           <t>L159: suspicious token(s): 35c (letter/digit mix) :: EGYPTIAN COTTON Ribbed Vests,2 for 35c.</t>
@@ -811,19 +799,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | symbol-only separator/garbage line :: 29 ，</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: alive and thatâ€™s all; Mr. Goold, a black-</t>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L176: isolated marker/symbol line :: A.</t>
+          <t>L106: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -838,13 +826,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -862,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -890,19 +878,15 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L207: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Algomaâ€”Some</t>
-        </is>
-      </c>
+          <t>L276: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •….</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L177: isolated marker/symbol line :: &amp;</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF06 FULLWIDTH AMPERSAND | isolated marker/symbol line :: ＆</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -917,13 +901,13 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
+          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -969,19 +953,15 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Hartley in a Most Revolting Lightâ€”The</t>
-        </is>
-      </c>
+          <t>L277: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L194: isolated marker/symbol line :: 54</t>
+          <t>L176: isolated marker/symbol line :: A.</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1000,11 +980,7 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
-        </is>
-      </c>
+      <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1048,19 +1024,15 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Attorney-Generalâ€™s Department, decided</t>
-        </is>
-      </c>
+          <t>L278: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L195: isolated marker/symbol line :: 5 \</t>
+          <t>L177: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1095,12 +1067,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr"/>
@@ -1119,24 +1091,20 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: house is my own and I donâ€™t care";</t>
-        </is>
-      </c>
+          <t>L319: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L196: isolated marker/symbol line :: 22</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | symbol-only separator/garbage line :: 29 ，</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1190,24 +1158,20 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L219: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wouldnâ€™t, and did not for about four</t>
-        </is>
-      </c>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | possible duplicated/overlap line with previous line (similarity 64%) :: South Brant ； Mr. Balfour over 800 in</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L197: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L194: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1237,12 +1201,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1261,24 +1225,20 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
-        </is>
-      </c>
+          <t>L469: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Blouses, nicely made, with sailor collar ； different patterns, all sizes. We will sell this lot at</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L198: isolated marker/symbol line :: .*.</t>
+          <t>L195: isolated marker/symbol line :: 5 \</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1313,7 +1273,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1327,29 +1287,25 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
+          <t>L331: suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-—</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
-        </is>
-      </c>
+          <t>L473: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L199: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L196: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1379,12 +1335,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1403,24 +1359,20 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
-        </is>
-      </c>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+606F CJK UNIFIED IDEOGRAPH-606F, U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 息 。</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L197: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
+          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1469,29 +1421,25 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "85c Saltfleet 1" :: â€”____________________=85c. â€” â€”________________</t>
+          <t>L477: suspicious token(s): 85c (letter/digit mix) :: —____________________=85c. — —________________</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
-        </is>
-      </c>
+          <t>L588: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L201: isolated marker/symbol line :: .</t>
+          <t>L198: isolated marker/symbol line :: .*.</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
+          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1501,7 +1449,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1526,7 +1474,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1545,24 +1493,20 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L425: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 876 fringed in Haldimand, and Mr. Sennâ€™s</t>
-        </is>
-      </c>
+          <t>L688: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L202: isolated marker/symbol line :: 46</t>
+          <t>L199: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
+          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -1611,29 +1555,25 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>L576: suspicious token(s): canidaton25 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "holidays" vs "Come nd canidaton25 better matched out after" :: the Come nd canidaton25</t>
+          <t>L576: suspicious token(s): canidaton25 (letter/digit mix) :: the Come nd canidaton25</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nipissing ; Mr. Bronson and Mr. Oâ€™Keefe</t>
-        </is>
-      </c>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L203: isolated marker/symbol line :: 50</t>
+          <t>L200: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L305: isolated marker/symbol line :: 50</t>
+          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1687,24 +1627,20 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "85c Saltfleet 1" :: â€”____________________=85c. â€” â€”________________</t>
-        </is>
-      </c>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L204: isolated marker/symbol line :: #.</t>
+          <t>L201: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: 54</t>
+          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1754,24 +1690,20 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L240: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: canvassersâ€™ reports when men vote under</t>
-        </is>
-      </c>
+          <t>L888: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: cott ； Mr. Robillard nearly 600 in Rus-</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L205: isolated marker/symbol line :: .</t>
+          <t>L202: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L308: isolated marker/symbol line :: 46</t>
+          <t>L305: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1807,26 +1739,18 @@
           <t>L655: suspicious token(s): 124c (letter/digit mix) :: at 3 for 124c, will be continued this week. This/</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L241: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: most of Adamâ€™sdescendants, they base</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L206: isolated marker/symbol line :: .</t>
+          <t>L203: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L309: symbol-only separator/garbage line :: . 67</t>
+          <t>L307: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1854,7 +1778,7 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>L517: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print BLOUSESâ€”40c,for 29c; 50c,for 39c;75c,</t>
+          <t>L517: suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print BLOUSES—40c,for 29c; 50c,for 39c;75c,</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
@@ -1862,26 +1786,18 @@
           <t>L656: suspicious token(s): 10c (letter/digit mix) :: marvelous bargain. They are worth 10c</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L243: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: she said if I wouldnâ€™t she would have</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L208: isolated marker/symbol line :: .</t>
+          <t>L204: isolated marker/symbol line :: #.</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L310: symbol-only separator/garbage line :: .125</t>
+          <t>L308: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1917,26 +1833,18 @@
           <t>L669: suspicious token(s): 123c (letter/digit mix) :: ful goods, 10 and 123c each, extra quality at 15</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to Quiggâ€™s, and the boys got beer and</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L209: isolated marker/symbol line :: ;</t>
+          <t>L205: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L311: symbol-only separator/garbage line :: .123</t>
+          <t>L309: symbol-only separator/garbage line :: . 67</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1969,29 +1877,21 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L253: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: can take it out inâ€™that way"; it was</t>
-        </is>
-      </c>
+          <t>L670: suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladies’ Balbriggan Vests. Men 8</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L210: isolated marker/symbol line :: .</t>
+          <t>L206: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L312: symbol-only separator/garbage line :: .80</t>
+          <t>L310: symbol-only separator/garbage line :: .125</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -2027,26 +1927,18 @@
           <t>L678: suspicious token(s): Stripe1Bathing (letter/digit mix) :: selling off at big reductions. Stripe1Bathing</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: each. Finch Bros.â€™ is the house for these goods.</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L207: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L313: symbol-only separator/garbage line :: .90</t>
+          <t>L311: symbol-only separator/garbage line :: .123</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -2082,26 +1974,18 @@
           <t>L679: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix) :: Flannels 39c, worth 65c. Plain French Twill</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L660: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: seasonâ€™s, but we have made deep cuts in the</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L208: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L314: symbol-only separator/garbage line :: .40</t>
+          <t>L312: symbol-only separator/garbage line :: .80</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2137,26 +2021,18 @@
           <t>L680: suspicious token(s): 25c (letter/digit mix), 40c (letter/digit mix) :: Bathing Flannel 25c, worth 40c. Childrens</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L213: isolated marker/symbol line :: 2</t>
+          <t>L209: isolated marker/symbol line :: ;</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 44</t>
+          <t>L313: symbol-only separator/garbage line :: .90</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2189,29 +2065,21 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Drawers. Ladiesâ€™ and Men's Hostery. Child-</t>
-        </is>
-      </c>
+          <t>L684: suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blouses—40c, for 29c; 50c, for 39c; 75c,</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L210: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: 77</t>
+          <t>L314: symbol-only separator/garbage line :: .40</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2247,26 +2115,18 @@
           <t>L685: suspicious token(s): 50c (letter/digit mix), 40c (letter/digit mix), 25c (letter/digit mix), 50c (letter/digit mix) :: for 50c. White Lawn Blouses 40c, for 25c. 50c</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦.</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L215: isolated marker/symbol line :: 67</t>
+          <t>L211: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L322: isolated marker/symbol line :: 13</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2302,26 +2162,18 @@
           <t>L686: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix), 49c (letter/digit mix), 70c (letter/digit mix), 59c (letter/digit mix) :: - Blouses 39c. 65c Blouses 49c. 70c Blouses 59c.</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at the house at 4 oâ€™clock ; when I got</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L216: isolated marker/symbol line :: 44</t>
+          <t>L212: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L324: isolated marker/symbol line :: 41</t>
+          <t>L318: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2357,26 +2209,18 @@
           <t>L703: suspicious token(s): 25c (letter/digit mix), 22c (letter/digit mix) :: extra large, 3 for 25c and 2 for 22c. Beach</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L278: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L217: symbol-only separator/garbage line :: 12845</t>
+          <t>L213: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: 16</t>
+          <t>L320: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2412,26 +2256,18 @@
           <t>L736: suspicious token(s): 25c (letter/digit mix) :: Fine Dress Sateens 20 and 25c, nowselling off</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L279: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BERTRAMâ€™S</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L218: isolated marker/symbol line :: '</t>
+          <t>L214: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L327: symbol-only separator/garbage line :: 21%</t>
+          <t>L322: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2467,26 +2303,18 @@
           <t>L738: suspicious token(s): 15c (letter/digit mix) :: 15c. all new styles. Handsome Broche Sateens</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: toriousâ€”being mistaken or classed together</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L219: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L215: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L329: symbol-only separator/garbage line :: 631 284</t>
+          <t>L324: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2519,29 +2347,21 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L824: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: with _. but weâ€™ve said enough on this subject</t>
-        </is>
-      </c>
+          <t>L839: suspicious token(s): 33Women’s (letter/digit mix) :: Our $1.33Women’s Strapor Tie Slippers we can</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L216: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L326: isolated marker/symbol line :: 16</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2577,26 +2397,18 @@
           <t>L847: suspicious token(s): Our32 (letter/digit mix) :: Our32.25 Men's Laced or Congress Boots we</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRINT BLOUSES.â€” We have just marked and put in stock 24 dozen Print</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L217: symbol-only separator/garbage line :: 12845</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
+          <t>L327: symbol-only separator/garbage line :: 21%</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2632,26 +2444,18 @@
           <t>L946: punctuation artifact: repeated exclamation marks | suspicious token(s): PUI0 (letter/digit mix) :: KIIW an Ma PUI0 ua!!!!setive A . aO</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L517: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print BLOUSESâ€”40c,for 29c; 50c,for 39c;75c,</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.35 Womenâ€™s Dongola Oxford Tie Shoes</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L222: isolated marker/symbol line :: .</t>
+          <t>L218: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
+          <t>L329: symbol-only separator/garbage line :: 631 284</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2679,26 +2483,18 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our 83 75 Menâ€™s Shell Cordovan Congress and</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: .</t>
+          <t>L219: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2726,26 +2522,18 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L850: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.75 Menâ€™s Laced Boots wo can prove to</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L224: isolated marker/symbol line :: 77</t>
+          <t>L220: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2773,26 +2561,18 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: in Fred coming home, he couldnâ€™t do</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L225: isolated marker/symbol line :: 125</t>
+          <t>L221: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
+          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2820,26 +2600,18 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00AF MACRON, U+20AC EURO SIGN :: æ�¯ ã€‚</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L997: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Branch Office, 31 King west, â€˜Phone 978</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L226: isolated marker/symbol line :: .</t>
+          <t>L222: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 57</t>
+          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2867,26 +2639,18 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L1054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and gentsâ€™, smoking</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L223: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: 29</t>
+          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2914,26 +2678,18 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L1060: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ADVERTISE IN THE TIMESâ€”</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L228: isolated marker/symbol line :: Â·</t>
+          <t>L224: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: 12</t>
+          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2961,26 +2717,18 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L1062: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L225: isolated marker/symbol line :: 125</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 46</t>
+          <t>L351: isolated marker/symbol line :: 57</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -3008,22 +2756,18 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L230: isolated marker/symbol line :: .</t>
+          <t>L226: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L359: isolated marker/symbol line :: 47</t>
+          <t>L353: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -3051,28 +2795,24 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L579: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L232: isolated marker/symbol line :: 0</t>
+          <t>L227: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: 51</t>
+          <t>L355: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
+          <t>L763: punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a d— of</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -3094,22 +2834,18 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L228: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 242</t>
+          <t>L357: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3137,22 +2873,18 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L234: isolated marker/symbol line :: 123</t>
+          <t>L229: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
+          <t>L359: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3176,22 +2908,18 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L235: isolated marker/symbol line :: 13</t>
+          <t>L230: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L367: symbol-only separator/garbage line :: .....30</t>
+          <t>L361: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3215,22 +2943,18 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L236: isolated marker/symbol line :: 18</t>
+          <t>L231: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L369: symbol-only separator/garbage line :: .....46</t>
+          <t>L363: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3254,22 +2978,18 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L591: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L237: isolated marker/symbol line :: .</t>
+          <t>L232: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L371: symbol-only separator/garbage line :: .....56</t>
+          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -3293,22 +3013,18 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L239: isolated marker/symbol line :: .</t>
+          <t>L233: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: .....34</t>
+          <t>L367: symbol-only separator/garbage line :: .....30</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3332,22 +3048,18 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L240: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L234: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
+          <t>L369: symbol-only separator/garbage line :: .....46</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3371,22 +3083,18 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L241: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L235: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L377: isolated marker/symbol line :: 250</t>
+          <t>L371: symbol-only separator/garbage line :: .....56</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -3410,22 +3118,18 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: .</t>
+          <t>L236: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: $1.75</t>
+          <t>L373: symbol-only separator/garbage line :: .....34</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3449,22 +3153,18 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L243: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L237: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
+          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3488,22 +3188,18 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L238: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
+          <t>L377: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3527,22 +3223,18 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L603: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L245: isolated marker/symbol line :: .</t>
+          <t>L239: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
+          <t>L385: symbol-only separator/garbage line :: $1.75</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
@@ -3566,22 +3258,18 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L246: isolated marker/symbol line :: .</t>
+          <t>L240: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: 67</t>
+          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3605,22 +3293,18 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L605: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L247: isolated marker/symbol line :: 80</t>
+          <t>L241: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: 78</t>
+          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3644,22 +3328,18 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L248: isolated marker/symbol line :: 41</t>
+          <t>L242: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L399: isolated marker/symbol line :: 54</t>
+          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3683,22 +3363,18 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L612: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L249: symbol-only separator/garbage line :: 45678</t>
+          <t>L243: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: 199</t>
+          <t>L395: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3722,22 +3398,18 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L613: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L250: isolated marker/symbol line :: 6</t>
+          <t>L244: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: a</t>
+          <t>L397: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3761,22 +3433,18 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L251: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L245: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
+          <t>L399: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3800,22 +3468,18 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L252: isolated marker/symbol line :: .</t>
+          <t>L246: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L405: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3839,22 +3503,18 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L622: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L253: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L247: isolated marker/symbol line :: 80</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
+          <t>L406: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3878,22 +3538,18 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L248: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L411: isolated marker/symbol line :: 195</t>
+          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3917,22 +3573,18 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L624: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L249: symbol-only separator/garbage line :: 45678</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
+          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3956,22 +3608,18 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L625: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L256: isolated marker/symbol line :: .</t>
+          <t>L250: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
+          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3995,22 +3643,18 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L626: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L257: isolated marker/symbol line :: 90</t>
+          <t>L251: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
+          <t>L411: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4034,22 +3678,18 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L258: isolated marker/symbol line :: 16</t>
+          <t>L252: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 44</t>
+          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4073,22 +3713,18 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L634: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L259: isolated marker/symbol line :: 7</t>
+          <t>L253: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 58</t>
+          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4112,22 +3748,18 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: .</t>
+          <t>L254: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 82</t>
+          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4151,22 +3783,18 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L261: isolated marker/symbol line :: 0</t>
+          <t>L255: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L469: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4190,22 +3818,18 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L638: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L262: isolated marker/symbol line :: .</t>
+          <t>L256: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
+          <t>L470: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4229,22 +3853,18 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L263: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L257: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
+          <t>L472: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4268,22 +3888,18 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L643: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L258: isolated marker/symbol line :: 16</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
+          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4307,22 +3923,18 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L644: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L265: isolated marker/symbol line :: .</t>
+          <t>L259: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
+          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4346,22 +3958,18 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L266: isolated marker/symbol line :: .</t>
+          <t>L260: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 92</t>
+          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4385,22 +3993,18 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L261: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: 95</t>
+          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4424,22 +4028,18 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L647: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L268: isolated marker/symbol line :: .</t>
+          <t>L262: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: 84</t>
+          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4463,22 +4063,18 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L650: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L269: isolated marker/symbol line :: 78</t>
+          <t>L263: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 44</t>
+          <t>L491: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4502,22 +4098,18 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L270: isolated marker/symbol line :: 46</t>
+          <t>L264: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L499: isolated marker/symbol line :: 61</t>
+          <t>L493: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4541,22 +4133,18 @@
       <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>L662: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L271: isolated marker/symbol line :: 21</t>
+          <t>L265: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
+          <t>L495: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4580,22 +4168,18 @@
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L272: isolated marker/symbol line :: 4</t>
+          <t>L266: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L503: isolated marker/symbol line :: 51</t>
+          <t>L497: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4619,22 +4203,18 @@
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L273: isolated marker/symbol line :: e</t>
+          <t>L267: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
+          <t>L499: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
@@ -4658,22 +4238,18 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L274: isolated marker/symbol line :: 6</t>
+          <t>L268: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
+          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
@@ -4697,22 +4273,18 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: 8</t>
+          <t>L269: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
+          <t>L503: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
@@ -4736,22 +4308,18 @@
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L270: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
@@ -4775,22 +4343,18 @@
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L281: isolated marker/symbol line :: .</t>
+          <t>L271: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L518: isolated marker/symbol line :: 276</t>
+          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
@@ -4814,22 +4378,18 @@
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L272: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
@@ -4853,20 +4413,20 @@
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L283: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O88" s="1" t="inlineStr"/>
+          <t>L273: isolated marker/symbol line :: e</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="inlineStr">
+        <is>
+          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr"/>
       <c r="R88" s="1" t="inlineStr"/>
@@ -4888,20 +4448,20 @@
       <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L284: isolated marker/symbol line :: 5</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr"/>
+          <t>L274: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="inlineStr">
+        <is>
+          <t>L518: isolated marker/symbol line :: 276</t>
+        </is>
+      </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr"/>
       <c r="R89" s="1" t="inlineStr"/>
@@ -4923,20 +4483,20 @@
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L414: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O90" s="1" t="inlineStr"/>
+          <t>L275: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="inlineStr">
+        <is>
+          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+        </is>
+      </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr"/>
       <c r="R90" s="1" t="inlineStr"/>
@@ -4958,20 +4518,20 @@
       <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>L683: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L415: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O91" s="1" t="inlineStr"/>
+          <t>L276: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •….</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="inlineStr">
+        <is>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
+        </is>
+      </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr"/>
       <c r="R91" s="1" t="inlineStr"/>
@@ -4993,17 +4553,13 @@
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L461: symbol-only separator/garbage line :: $2.00</t>
+          <t>L277: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -5028,17 +4584,13 @@
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr">
-        <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J93" s="1" t="inlineStr"/>
       <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L466: isolated marker/symbol line :: 3</t>
+          <t>L278: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -5063,17 +4615,13 @@
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>L688: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦</t>
-        </is>
-      </c>
+      <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L467: symbol-only separator/garbage line :: $1.75</t>
+          <t>L279: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -5098,17 +4646,13 @@
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>L695: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 2</t>
+          <t>L280: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -5133,17 +4677,13 @@
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L481: symbol-only separator/garbage line :: $2.00</t>
+          <t>L281: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5168,17 +4708,13 @@
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L487: isolated marker/symbol line :: 2</t>
+          <t>L282: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5203,17 +4739,13 @@
       <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L488: isolated marker/symbol line :: 5</t>
+          <t>L283: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5238,17 +4770,13 @@
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>L701: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L536: isolated marker/symbol line :: '</t>
+          <t>L284: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5273,17 +4801,13 @@
       <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>L702: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L537: isolated marker/symbol line :: f</t>
+          <t>L319: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5308,17 +4832,13 @@
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L554: isolated marker/symbol line :: 631</t>
+          <t>L414: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5343,17 +4863,13 @@
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L555: isolated marker/symbol line :: 284</t>
+          <t>L415: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5378,17 +4894,13 @@
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J103" s="1" t="inlineStr"/>
       <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: 43</t>
+          <t>L461: symbol-only separator/garbage line :: $2.00</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5413,17 +4925,13 @@
       <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L558: isolated marker/symbol line :: 57</t>
+          <t>L466: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5448,17 +4956,13 @@
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>L721: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L559: isolated marker/symbol line :: .</t>
+          <t>L467: symbol-only separator/garbage line :: $1.75</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5483,17 +4987,13 @@
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: .</t>
+          <t>L472: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5518,17 +5018,13 @@
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L562: isolated marker/symbol line :: .</t>
+          <t>L473: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5553,17 +5049,13 @@
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦ 1, 551</t>
-        </is>
-      </c>
+      <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L481: symbol-only separator/garbage line :: $2.00</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5588,17 +5080,13 @@
       <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>L739: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L487: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5623,17 +5111,13 @@
       <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>L740: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 30</t>
+          <t>L488: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5658,17 +5142,13 @@
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>L741: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: 29</t>
+          <t>L536: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5693,17 +5173,13 @@
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>L769: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: said it's a h â€”- of a note or a d â€”- of</t>
-        </is>
-      </c>
+      <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L567: isolated marker/symbol line :: 8</t>
+          <t>L537: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5728,17 +5204,13 @@
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L569: isolated marker/symbol line :: #</t>
+          <t>L554: isolated marker/symbol line :: 631</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5763,17 +5235,13 @@
       <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>L952: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gentsâ€™Blouses,</t>
-        </is>
-      </c>
+      <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L570: isolated marker/symbol line :: #</t>
+          <t>L555: isolated marker/symbol line :: 284</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5798,17 +5266,13 @@
       <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>L1064: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ã€Œ</t>
-        </is>
-      </c>
+      <c r="J115" s="1" t="inlineStr"/>
       <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L572: isolated marker/symbol line :: .</t>
+          <t>L557: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5839,7 +5303,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L558: isolated marker/symbol line :: 57</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5870,7 +5334,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L559: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5901,7 +5365,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L575: isolated marker/symbol line :: 46</t>
+          <t>L560: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5932,7 +5396,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L576: isolated marker/symbol line :: 12</t>
+          <t>L561: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5963,7 +5427,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: .</t>
+          <t>L562: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5994,7 +5458,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L579: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L563: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -6025,7 +5489,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L564: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -6056,7 +5520,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L581: isolated marker/symbol line :: .</t>
+          <t>L565: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -6087,7 +5551,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L582: isolated marker/symbol line :: .</t>
+          <t>L566: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -6118,7 +5582,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L567: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -6149,7 +5613,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+606F CJK UNIFIED IDEOGRAPH-606F, U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 息 。</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6180,7 +5644,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L585: symbol-only separator/garbage line :: 108456</t>
+          <t>L569: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6211,7 +5675,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L586: isolated marker/symbol line :: 56</t>
+          <t>L570: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6242,7 +5706,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: 46</t>
+          <t>L571: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6273,7 +5737,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L589: isolated marker/symbol line :: .</t>
+          <t>L572: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6304,7 +5768,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L590: isolated marker/symbol line :: .</t>
+          <t>L573: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6335,7 +5799,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L574: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6366,7 +5830,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L575: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6397,7 +5861,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L576: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6428,7 +5892,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L577: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6459,7 +5923,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L596: isolated marker/symbol line :: .</t>
+          <t>L578: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6490,7 +5954,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L597: isolated marker/symbol line :: 34</t>
+          <t>L579: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6521,7 +5985,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L598: isolated marker/symbol line :: 47</t>
+          <t>L580: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6552,7 +6016,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L599: isolated marker/symbol line :: 0</t>
+          <t>L581: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6583,7 +6047,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L600: isolated marker/symbol line :: 0</t>
+          <t>L582: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6614,7 +6078,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L583: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6645,7 +6109,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L584: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6676,7 +6140,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L603: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L585: symbol-only separator/garbage line :: 108456</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6707,7 +6171,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L586: isolated marker/symbol line :: 56</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6738,7 +6202,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L605: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L587: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6769,7 +6233,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L588: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6800,7 +6264,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L607: isolated marker/symbol line :: 35</t>
+          <t>L589: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6831,7 +6295,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L608: isolated marker/symbol line :: 51</t>
+          <t>L590: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6862,7 +6326,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L609: isolated marker/symbol line :: 0</t>
+          <t>L591: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6893,7 +6357,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L610: isolated marker/symbol line :: .</t>
+          <t>L592: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6924,7 +6388,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L611: isolated marker/symbol line :: Â·.</t>
+          <t>L593: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6955,7 +6419,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L612: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L594: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6986,7 +6450,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L613: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L595: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -7017,7 +6481,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L596: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -7048,7 +6512,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L597: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -7079,7 +6543,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L616: isolated marker/symbol line :: .</t>
+          <t>L598: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -7110,7 +6574,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L617: isolated marker/symbol line :: 250</t>
+          <t>L599: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -7141,7 +6605,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L618: isolated marker/symbol line :: 242</t>
+          <t>L600: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -7172,7 +6636,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L620: isolated marker/symbol line :: 07</t>
+          <t>L601: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -7203,7 +6667,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L621: isolated marker/symbol line :: 67</t>
+          <t>L602: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -7234,7 +6698,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L625: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L603: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -7265,7 +6729,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L626: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L604: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7296,7 +6760,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: 78</t>
+          <t>L605: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7327,7 +6791,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L629: isolated marker/symbol line :: 52</t>
+          <t>L606: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7358,7 +6822,7 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L630: isolated marker/symbol line :: 128</t>
+          <t>L607: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7389,7 +6853,7 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L631: isolated marker/symbol line :: 123</t>
+          <t>L608: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7420,7 +6884,7 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L632: isolated marker/symbol line :: #.</t>
+          <t>L609: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7451,7 +6915,7 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L633: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L610: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7482,7 +6946,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L635: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L611: isolated marker/symbol line :: ·.</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7513,7 +6977,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L612: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7544,7 +7008,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L613: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7575,7 +7039,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L638: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L614: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7606,7 +7070,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L615: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7637,7 +7101,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L640: isolated marker/symbol line :: 54</t>
+          <t>L616: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7668,7 +7132,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L641: isolated marker/symbol line :: 45</t>
+          <t>L617: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -7699,7 +7163,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: .</t>
+          <t>L618: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -7730,7 +7194,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L643: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L620: isolated marker/symbol line :: 07</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -7761,7 +7225,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L621: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -7792,7 +7256,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L622: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -7823,7 +7287,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L647: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L623: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -7854,7 +7318,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L648: isolated marker/symbol line :: .</t>
+          <t>L624: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -7885,7 +7349,7 @@
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L649: isolated marker/symbol line :: .</t>
+          <t>L625: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -7916,7 +7380,7 @@
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L650: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L626: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -7947,7 +7411,7 @@
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L651: isolated marker/symbol line :: 199</t>
+          <t>L627: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -7978,7 +7442,7 @@
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L652: isolated marker/symbol line :: 164</t>
+          <t>L628: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -8009,7 +7473,7 @@
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L653: isolated marker/symbol line :: 0</t>
+          <t>L629: isolated marker/symbol line :: 52</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -8040,7 +7504,7 @@
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L655: isolated marker/symbol line :: 63</t>
+          <t>L630: isolated marker/symbol line :: 128</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -8071,7 +7535,7 @@
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L656: isolated marker/symbol line :: 44</t>
+          <t>L631: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -8102,7 +7566,7 @@
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L657: isolated marker/symbol line :: 0</t>
+          <t>L632: isolated marker/symbol line :: #.</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -8133,7 +7597,7 @@
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L658: isolated marker/symbol line :: e</t>
+          <t>L633: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -8164,7 +7628,7 @@
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L659: isolated marker/symbol line :: . 0</t>
+          <t>L634: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -8195,7 +7659,7 @@
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L660: isolated marker/symbol line :: 1</t>
+          <t>L635: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -8226,7 +7690,7 @@
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L636: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -8257,7 +7721,7 @@
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L637: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -8288,7 +7752,7 @@
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
         <is>
-          <t>L667: isolated marker/symbol line :: 71</t>
+          <t>L638: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O195" s="1" t="inlineStr"/>
@@ -8319,7 +7783,7 @@
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: 58</t>
+          <t>L639: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O196" s="1" t="inlineStr"/>
@@ -8350,7 +7814,7 @@
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
         <is>
-          <t>L669: isolated marker/symbol line :: 123</t>
+          <t>L640: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O197" s="1" t="inlineStr"/>
@@ -8381,7 +7845,7 @@
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
         <is>
-          <t>L670: isolated marker/symbol line :: .</t>
+          <t>L641: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="O198" s="1" t="inlineStr"/>
@@ -8412,7 +7876,7 @@
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
         <is>
-          <t>L671: isolated marker/symbol line :: 0</t>
+          <t>L642: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O199" s="1" t="inlineStr"/>
@@ -8443,7 +7907,7 @@
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
         <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L643: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O200" s="1" t="inlineStr"/>
@@ -8474,7 +7938,7 @@
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
         <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L644: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O201" s="1" t="inlineStr"/>
@@ -8505,7 +7969,7 @@
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
         <is>
-          <t>L674: isolated marker/symbol line :: .</t>
+          <t>L645: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O202" s="1" t="inlineStr"/>
@@ -8536,7 +8000,7 @@
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
         <is>
-          <t>L675: isolated marker/symbol line :: .</t>
+          <t>L646: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O203" s="1" t="inlineStr"/>
@@ -8567,7 +8031,7 @@
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
         <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L647: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O204" s="1" t="inlineStr"/>
@@ -8598,7 +8062,7 @@
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
         <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L648: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O205" s="1" t="inlineStr"/>
@@ -8629,7 +8093,7 @@
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
         <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L649: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O206" s="1" t="inlineStr"/>
@@ -8660,7 +8124,7 @@
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
         <is>
-          <t>L680: isolated marker/symbol line :: 0</t>
+          <t>L650: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O207" s="1" t="inlineStr"/>
@@ -8691,7 +8155,7 @@
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
         <is>
-          <t>L681: isolated marker/symbol line :: 61</t>
+          <t>L651: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="O208" s="1" t="inlineStr"/>
@@ -8722,7 +8186,7 @@
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
         <is>
-          <t>L682: isolated marker/symbol line :: 82</t>
+          <t>L652: isolated marker/symbol line :: 164</t>
         </is>
       </c>
       <c r="O209" s="1" t="inlineStr"/>
@@ -8753,7 +8217,7 @@
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
         <is>
-          <t>L683: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L653: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O210" s="1" t="inlineStr"/>
@@ -8784,7 +8248,7 @@
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
         <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L655: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O211" s="1" t="inlineStr"/>
@@ -8815,7 +8279,7 @@
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
         <is>
-          <t>L685: isolated marker/symbol line :: .</t>
+          <t>L656: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O212" s="1" t="inlineStr"/>
@@ -8846,7 +8310,7 @@
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
         <is>
-          <t>L686: isolated marker/symbol line :: .</t>
+          <t>L657: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O213" s="1" t="inlineStr"/>
@@ -8877,7 +8341,7 @@
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
         <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L658: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O214" s="1" t="inlineStr"/>
@@ -8908,7 +8372,7 @@
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
         <is>
-          <t>L689: isolated marker/symbol line :: 195</t>
+          <t>L659: isolated marker/symbol line :: . 0</t>
         </is>
       </c>
       <c r="O215" s="1" t="inlineStr"/>
@@ -8939,7 +8403,7 @@
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
         <is>
-          <t>L690: isolated marker/symbol line :: 184</t>
+          <t>L660: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O216" s="1" t="inlineStr"/>
@@ -8970,7 +8434,7 @@
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
         <is>
-          <t>L692: isolated marker/symbol line :: 73</t>
+          <t>L661: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O217" s="1" t="inlineStr"/>
@@ -9001,7 +8465,7 @@
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
         <is>
-          <t>L693: isolated marker/symbol line :: 92</t>
+          <t>L662: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O218" s="1" t="inlineStr"/>
@@ -9032,7 +8496,7 @@
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
         <is>
-          <t>L694: isolated marker/symbol line :: .</t>
+          <t>L663: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O219" s="1" t="inlineStr"/>
@@ -9063,7 +8527,7 @@
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
         <is>
-          <t>L695: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L664: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O220" s="1" t="inlineStr"/>
@@ -9094,7 +8558,7 @@
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
         <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L665: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O221" s="1" t="inlineStr"/>
@@ -9125,7 +8589,7 @@
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
         <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L666: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O222" s="1" t="inlineStr"/>
@@ -9156,7 +8620,7 @@
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
         <is>
-          <t>L698: isolated marker/symbol line :: 51</t>
+          <t>L667: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O223" s="1" t="inlineStr"/>
@@ -9187,7 +8651,7 @@
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
         <is>
-          <t>L699: isolated marker/symbol line :: 95</t>
+          <t>L668: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O224" s="1" t="inlineStr"/>
@@ -9218,7 +8682,7 @@
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
         <is>
-          <t>L701: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L669: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O225" s="1" t="inlineStr"/>
@@ -9249,7 +8713,7 @@
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
         <is>
-          <t>L702: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L670: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O226" s="1" t="inlineStr"/>
@@ -9280,7 +8744,7 @@
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L671: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O227" s="1" t="inlineStr"/>
@@ -9311,7 +8775,7 @@
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
         <is>
-          <t>L704: isolated marker/symbol line :: 4</t>
+          <t>L672: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O228" s="1" t="inlineStr"/>
@@ -9342,7 +8806,7 @@
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
         <is>
-          <t>L705: isolated marker/symbol line :: 29</t>
+          <t>L673: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O229" s="1" t="inlineStr"/>
@@ -9373,7 +8837,7 @@
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
         <is>
-          <t>L706: isolated marker/symbol line :: 84</t>
+          <t>L674: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O230" s="1" t="inlineStr"/>
@@ -9404,7 +8868,7 @@
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
         <is>
-          <t>L707: symbol-only separator/garbage line :: 12845</t>
+          <t>L675: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O231" s="1" t="inlineStr"/>
@@ -9435,7 +8899,7 @@
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
         <is>
-          <t>L708: isolated marker/symbol line :: #.</t>
+          <t>L676: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O232" s="1" t="inlineStr"/>
@@ -9466,7 +8930,7 @@
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
         <is>
-          <t>L709: isolated marker/symbol line :: .</t>
+          <t>L677: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O233" s="1" t="inlineStr"/>
@@ -9497,7 +8961,7 @@
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
         <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L678: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O234" s="1" t="inlineStr"/>
@@ -9528,7 +8992,7 @@
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
         <is>
-          <t>L711: isolated marker/symbol line :: 59</t>
+          <t>L679: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O235" s="1" t="inlineStr"/>
@@ -9559,7 +9023,7 @@
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: 44</t>
+          <t>L680: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O236" s="1" t="inlineStr"/>
@@ -9590,7 +9054,7 @@
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
         <is>
-          <t>L713: isolated marker/symbol line :: .</t>
+          <t>L681: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O237" s="1" t="inlineStr"/>
@@ -9621,7 +9085,7 @@
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
         <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L682: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="O238" s="1" t="inlineStr"/>
@@ -9652,7 +9116,7 @@
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
         <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L683: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O239" s="1" t="inlineStr"/>
@@ -9683,7 +9147,7 @@
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
         <is>
-          <t>L716: isolated marker/symbol line :: .</t>
+          <t>L684: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O240" s="1" t="inlineStr"/>
@@ -9714,7 +9178,7 @@
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
         <is>
-          <t>L717: symbol-only separator/garbage line :: #. 0</t>
+          <t>L685: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O241" s="1" t="inlineStr"/>
@@ -9745,7 +9209,7 @@
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
         <is>
-          <t>L718: isolated marker/symbol line :: 61</t>
+          <t>L686: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O242" s="1" t="inlineStr"/>
@@ -9776,7 +9240,7 @@
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
         <is>
-          <t>L719: isolated marker/symbol line :: 64</t>
+          <t>L687: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O243" s="1" t="inlineStr"/>
@@ -9807,7 +9271,7 @@
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
         <is>
-          <t>L720: isolated marker/symbol line :: 4</t>
+          <t>L688: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
         </is>
       </c>
       <c r="O244" s="1" t="inlineStr"/>
@@ -9838,7 +9302,7 @@
       <c r="M245" s="1" t="inlineStr"/>
       <c r="N245" s="1" t="inlineStr">
         <is>
-          <t>L721: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L689: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="O245" s="1" t="inlineStr"/>
@@ -9869,7 +9333,7 @@
       <c r="M246" s="1" t="inlineStr"/>
       <c r="N246" s="1" t="inlineStr">
         <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L690: isolated marker/symbol line :: 184</t>
         </is>
       </c>
       <c r="O246" s="1" t="inlineStr"/>
@@ -9900,7 +9364,7 @@
       <c r="M247" s="1" t="inlineStr"/>
       <c r="N247" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L692: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O247" s="1" t="inlineStr"/>
@@ -9931,7 +9395,7 @@
       <c r="M248" s="1" t="inlineStr"/>
       <c r="N248" s="1" t="inlineStr">
         <is>
-          <t>L725: isolated marker/symbol line :: .</t>
+          <t>L693: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O248" s="1" t="inlineStr"/>
@@ -9962,7 +9426,7 @@
       <c r="M249" s="1" t="inlineStr"/>
       <c r="N249" s="1" t="inlineStr">
         <is>
-          <t>L726: isolated marker/symbol line :: .</t>
+          <t>L694: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O249" s="1" t="inlineStr"/>
@@ -9993,7 +9457,7 @@
       <c r="M250" s="1" t="inlineStr"/>
       <c r="N250" s="1" t="inlineStr">
         <is>
-          <t>L727: isolated marker/symbol line :: 0.</t>
+          <t>L695: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O250" s="1" t="inlineStr"/>
@@ -10024,7 +9488,7 @@
       <c r="M251" s="1" t="inlineStr"/>
       <c r="N251" s="1" t="inlineStr">
         <is>
-          <t>L728: isolated marker/symbol line :: 0</t>
+          <t>L696: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr"/>
@@ -10055,7 +9519,7 @@
       <c r="M252" s="1" t="inlineStr"/>
       <c r="N252" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: 276</t>
+          <t>L697: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr"/>
@@ -10086,7 +9550,7 @@
       <c r="M253" s="1" t="inlineStr"/>
       <c r="N253" s="1" t="inlineStr">
         <is>
-          <t>L730: isolated marker/symbol line :: 376</t>
+          <t>L698: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr"/>
@@ -10117,7 +9581,7 @@
       <c r="M254" s="1" t="inlineStr"/>
       <c r="N254" s="1" t="inlineStr">
         <is>
-          <t>L731: isolated marker/symbol line :: *</t>
+          <t>L699: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr"/>
@@ -10148,7 +9612,7 @@
       <c r="M255" s="1" t="inlineStr"/>
       <c r="N255" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: R</t>
+          <t>L700: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O255" s="1" t="inlineStr"/>
@@ -10179,7 +9643,7 @@
       <c r="M256" s="1" t="inlineStr"/>
       <c r="N256" s="1" t="inlineStr">
         <is>
-          <t>L734: symbol-only separator/garbage line :: 1, 250</t>
+          <t>L701: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O256" s="1" t="inlineStr"/>
@@ -10210,7 +9674,7 @@
       <c r="M257" s="1" t="inlineStr"/>
       <c r="N257" s="1" t="inlineStr">
         <is>
-          <t>L736: isolated marker/symbol line :: 4</t>
+          <t>L702: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O257" s="1" t="inlineStr"/>
@@ -10241,7 +9705,7 @@
       <c r="M258" s="1" t="inlineStr"/>
       <c r="N258" s="1" t="inlineStr">
         <is>
-          <t>L738: isolated marker/symbol line :: .</t>
+          <t>L703: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O258" s="1" t="inlineStr"/>
@@ -10272,7 +9736,7 @@
       <c r="M259" s="1" t="inlineStr"/>
       <c r="N259" s="1" t="inlineStr">
         <is>
-          <t>L739: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L704: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr"/>
@@ -10303,7 +9767,7 @@
       <c r="M260" s="1" t="inlineStr"/>
       <c r="N260" s="1" t="inlineStr">
         <is>
-          <t>L740: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L705: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr"/>
@@ -10334,7 +9798,7 @@
       <c r="M261" s="1" t="inlineStr"/>
       <c r="N261" s="1" t="inlineStr">
         <is>
-          <t>L741: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L706: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr"/>
@@ -10365,7 +9829,7 @@
       <c r="M262" s="1" t="inlineStr"/>
       <c r="N262" s="1" t="inlineStr">
         <is>
-          <t>L742: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L707: symbol-only separator/garbage line :: 12845</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr"/>
@@ -10396,7 +9860,7 @@
       <c r="M263" s="1" t="inlineStr"/>
       <c r="N263" s="1" t="inlineStr">
         <is>
-          <t>L745: isolated marker/symbol line :: w</t>
+          <t>L708: isolated marker/symbol line :: #.</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr"/>
@@ -10427,7 +9891,7 @@
       <c r="M264" s="1" t="inlineStr"/>
       <c r="N264" s="1" t="inlineStr">
         <is>
-          <t>L747: isolated marker/symbol line :: 2</t>
+          <t>L709: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O264" s="1" t="inlineStr"/>
@@ -10458,7 +9922,7 @@
       <c r="M265" s="1" t="inlineStr"/>
       <c r="N265" s="1" t="inlineStr">
         <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L710: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O265" s="1" t="inlineStr"/>
@@ -10489,7 +9953,7 @@
       <c r="M266" s="1" t="inlineStr"/>
       <c r="N266" s="1" t="inlineStr">
         <is>
-          <t>L849: isolated marker/symbol line :: D</t>
+          <t>L711: isolated marker/symbol line :: 59</t>
         </is>
       </c>
       <c r="O266" s="1" t="inlineStr"/>
@@ -10520,7 +9984,7 @@
       <c r="M267" s="1" t="inlineStr"/>
       <c r="N267" s="1" t="inlineStr">
         <is>
-          <t>L967: isolated marker/symbol line :: 18</t>
+          <t>L712: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O267" s="1" t="inlineStr"/>
@@ -10551,7 +10015,7 @@
       <c r="M268" s="1" t="inlineStr"/>
       <c r="N268" s="1" t="inlineStr">
         <is>
-          <t>L969: isolated marker/symbol line :: 20</t>
+          <t>L713: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O268" s="1" t="inlineStr"/>
@@ -10582,7 +10046,7 @@
       <c r="M269" s="1" t="inlineStr"/>
       <c r="N269" s="1" t="inlineStr">
         <is>
-          <t>L991: symbol-only separator/garbage line :: $5.25</t>
+          <t>L714: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O269" s="1" t="inlineStr"/>
@@ -10613,7 +10077,7 @@
       <c r="M270" s="1" t="inlineStr"/>
       <c r="N270" s="1" t="inlineStr">
         <is>
-          <t>L993: isolated marker/symbol line :: c</t>
+          <t>L715: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O270" s="1" t="inlineStr"/>
@@ -10644,7 +10108,7 @@
       <c r="M271" s="1" t="inlineStr"/>
       <c r="N271" s="1" t="inlineStr">
         <is>
-          <t>L1008: isolated marker/symbol line :: d</t>
+          <t>L716: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O271" s="1" t="inlineStr"/>
@@ -10675,7 +10139,7 @@
       <c r="M272" s="1" t="inlineStr"/>
       <c r="N272" s="1" t="inlineStr">
         <is>
-          <t>L1038: symbol-only separator/garbage line :: $1.50.</t>
+          <t>L717: symbol-only separator/garbage line :: #. 0</t>
         </is>
       </c>
       <c r="O272" s="1" t="inlineStr"/>
@@ -10706,7 +10170,7 @@
       <c r="M273" s="1" t="inlineStr"/>
       <c r="N273" s="1" t="inlineStr">
         <is>
-          <t>L1089: isolated marker/symbol line :: *</t>
+          <t>L718: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O273" s="1" t="inlineStr"/>
@@ -10737,7 +10201,7 @@
       <c r="M274" s="1" t="inlineStr"/>
       <c r="N274" s="1" t="inlineStr">
         <is>
-          <t>L1090: isolated marker/symbol line :: 5</t>
+          <t>L719: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O274" s="1" t="inlineStr"/>
@@ -10752,6 +10216,1091 @@
       <c r="X274" s="1" t="inlineStr"/>
       <c r="Y274" s="1" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr"/>
+      <c r="B275" s="1" t="inlineStr"/>
+      <c r="C275" s="1" t="inlineStr"/>
+      <c r="D275" s="1" t="inlineStr"/>
+      <c r="E275" s="1" t="inlineStr"/>
+      <c r="F275" s="1" t="inlineStr"/>
+      <c r="G275" s="1" t="inlineStr"/>
+      <c r="H275" s="1" t="inlineStr"/>
+      <c r="I275" s="1" t="inlineStr"/>
+      <c r="J275" s="1" t="inlineStr"/>
+      <c r="K275" s="1" t="inlineStr"/>
+      <c r="L275" s="1" t="inlineStr"/>
+      <c r="M275" s="1" t="inlineStr"/>
+      <c r="N275" s="1" t="inlineStr">
+        <is>
+          <t>L720: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O275" s="1" t="inlineStr"/>
+      <c r="P275" s="1" t="inlineStr"/>
+      <c r="Q275" s="1" t="inlineStr"/>
+      <c r="R275" s="1" t="inlineStr"/>
+      <c r="S275" s="1" t="inlineStr"/>
+      <c r="T275" s="1" t="inlineStr"/>
+      <c r="U275" s="1" t="inlineStr"/>
+      <c r="V275" s="1" t="inlineStr"/>
+      <c r="W275" s="1" t="inlineStr"/>
+      <c r="X275" s="1" t="inlineStr"/>
+      <c r="Y275" s="1" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr"/>
+      <c r="B276" s="1" t="inlineStr"/>
+      <c r="C276" s="1" t="inlineStr"/>
+      <c r="D276" s="1" t="inlineStr"/>
+      <c r="E276" s="1" t="inlineStr"/>
+      <c r="F276" s="1" t="inlineStr"/>
+      <c r="G276" s="1" t="inlineStr"/>
+      <c r="H276" s="1" t="inlineStr"/>
+      <c r="I276" s="1" t="inlineStr"/>
+      <c r="J276" s="1" t="inlineStr"/>
+      <c r="K276" s="1" t="inlineStr"/>
+      <c r="L276" s="1" t="inlineStr"/>
+      <c r="M276" s="1" t="inlineStr"/>
+      <c r="N276" s="1" t="inlineStr">
+        <is>
+          <t>L721: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O276" s="1" t="inlineStr"/>
+      <c r="P276" s="1" t="inlineStr"/>
+      <c r="Q276" s="1" t="inlineStr"/>
+      <c r="R276" s="1" t="inlineStr"/>
+      <c r="S276" s="1" t="inlineStr"/>
+      <c r="T276" s="1" t="inlineStr"/>
+      <c r="U276" s="1" t="inlineStr"/>
+      <c r="V276" s="1" t="inlineStr"/>
+      <c r="W276" s="1" t="inlineStr"/>
+      <c r="X276" s="1" t="inlineStr"/>
+      <c r="Y276" s="1" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr"/>
+      <c r="B277" s="1" t="inlineStr"/>
+      <c r="C277" s="1" t="inlineStr"/>
+      <c r="D277" s="1" t="inlineStr"/>
+      <c r="E277" s="1" t="inlineStr"/>
+      <c r="F277" s="1" t="inlineStr"/>
+      <c r="G277" s="1" t="inlineStr"/>
+      <c r="H277" s="1" t="inlineStr"/>
+      <c r="I277" s="1" t="inlineStr"/>
+      <c r="J277" s="1" t="inlineStr"/>
+      <c r="K277" s="1" t="inlineStr"/>
+      <c r="L277" s="1" t="inlineStr"/>
+      <c r="M277" s="1" t="inlineStr"/>
+      <c r="N277" s="1" t="inlineStr">
+        <is>
+          <t>L722: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O277" s="1" t="inlineStr"/>
+      <c r="P277" s="1" t="inlineStr"/>
+      <c r="Q277" s="1" t="inlineStr"/>
+      <c r="R277" s="1" t="inlineStr"/>
+      <c r="S277" s="1" t="inlineStr"/>
+      <c r="T277" s="1" t="inlineStr"/>
+      <c r="U277" s="1" t="inlineStr"/>
+      <c r="V277" s="1" t="inlineStr"/>
+      <c r="W277" s="1" t="inlineStr"/>
+      <c r="X277" s="1" t="inlineStr"/>
+      <c r="Y277" s="1" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr"/>
+      <c r="B278" s="1" t="inlineStr"/>
+      <c r="C278" s="1" t="inlineStr"/>
+      <c r="D278" s="1" t="inlineStr"/>
+      <c r="E278" s="1" t="inlineStr"/>
+      <c r="F278" s="1" t="inlineStr"/>
+      <c r="G278" s="1" t="inlineStr"/>
+      <c r="H278" s="1" t="inlineStr"/>
+      <c r="I278" s="1" t="inlineStr"/>
+      <c r="J278" s="1" t="inlineStr"/>
+      <c r="K278" s="1" t="inlineStr"/>
+      <c r="L278" s="1" t="inlineStr"/>
+      <c r="M278" s="1" t="inlineStr"/>
+      <c r="N278" s="1" t="inlineStr">
+        <is>
+          <t>L723: isolated marker/symbol line :: ·…</t>
+        </is>
+      </c>
+      <c r="O278" s="1" t="inlineStr"/>
+      <c r="P278" s="1" t="inlineStr"/>
+      <c r="Q278" s="1" t="inlineStr"/>
+      <c r="R278" s="1" t="inlineStr"/>
+      <c r="S278" s="1" t="inlineStr"/>
+      <c r="T278" s="1" t="inlineStr"/>
+      <c r="U278" s="1" t="inlineStr"/>
+      <c r="V278" s="1" t="inlineStr"/>
+      <c r="W278" s="1" t="inlineStr"/>
+      <c r="X278" s="1" t="inlineStr"/>
+      <c r="Y278" s="1" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr"/>
+      <c r="B279" s="1" t="inlineStr"/>
+      <c r="C279" s="1" t="inlineStr"/>
+      <c r="D279" s="1" t="inlineStr"/>
+      <c r="E279" s="1" t="inlineStr"/>
+      <c r="F279" s="1" t="inlineStr"/>
+      <c r="G279" s="1" t="inlineStr"/>
+      <c r="H279" s="1" t="inlineStr"/>
+      <c r="I279" s="1" t="inlineStr"/>
+      <c r="J279" s="1" t="inlineStr"/>
+      <c r="K279" s="1" t="inlineStr"/>
+      <c r="L279" s="1" t="inlineStr"/>
+      <c r="M279" s="1" t="inlineStr"/>
+      <c r="N279" s="1" t="inlineStr">
+        <is>
+          <t>L724: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+        </is>
+      </c>
+      <c r="O279" s="1" t="inlineStr"/>
+      <c r="P279" s="1" t="inlineStr"/>
+      <c r="Q279" s="1" t="inlineStr"/>
+      <c r="R279" s="1" t="inlineStr"/>
+      <c r="S279" s="1" t="inlineStr"/>
+      <c r="T279" s="1" t="inlineStr"/>
+      <c r="U279" s="1" t="inlineStr"/>
+      <c r="V279" s="1" t="inlineStr"/>
+      <c r="W279" s="1" t="inlineStr"/>
+      <c r="X279" s="1" t="inlineStr"/>
+      <c r="Y279" s="1" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr"/>
+      <c r="B280" s="1" t="inlineStr"/>
+      <c r="C280" s="1" t="inlineStr"/>
+      <c r="D280" s="1" t="inlineStr"/>
+      <c r="E280" s="1" t="inlineStr"/>
+      <c r="F280" s="1" t="inlineStr"/>
+      <c r="G280" s="1" t="inlineStr"/>
+      <c r="H280" s="1" t="inlineStr"/>
+      <c r="I280" s="1" t="inlineStr"/>
+      <c r="J280" s="1" t="inlineStr"/>
+      <c r="K280" s="1" t="inlineStr"/>
+      <c r="L280" s="1" t="inlineStr"/>
+      <c r="M280" s="1" t="inlineStr"/>
+      <c r="N280" s="1" t="inlineStr">
+        <is>
+          <t>L725: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O280" s="1" t="inlineStr"/>
+      <c r="P280" s="1" t="inlineStr"/>
+      <c r="Q280" s="1" t="inlineStr"/>
+      <c r="R280" s="1" t="inlineStr"/>
+      <c r="S280" s="1" t="inlineStr"/>
+      <c r="T280" s="1" t="inlineStr"/>
+      <c r="U280" s="1" t="inlineStr"/>
+      <c r="V280" s="1" t="inlineStr"/>
+      <c r="W280" s="1" t="inlineStr"/>
+      <c r="X280" s="1" t="inlineStr"/>
+      <c r="Y280" s="1" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr"/>
+      <c r="B281" s="1" t="inlineStr"/>
+      <c r="C281" s="1" t="inlineStr"/>
+      <c r="D281" s="1" t="inlineStr"/>
+      <c r="E281" s="1" t="inlineStr"/>
+      <c r="F281" s="1" t="inlineStr"/>
+      <c r="G281" s="1" t="inlineStr"/>
+      <c r="H281" s="1" t="inlineStr"/>
+      <c r="I281" s="1" t="inlineStr"/>
+      <c r="J281" s="1" t="inlineStr"/>
+      <c r="K281" s="1" t="inlineStr"/>
+      <c r="L281" s="1" t="inlineStr"/>
+      <c r="M281" s="1" t="inlineStr"/>
+      <c r="N281" s="1" t="inlineStr">
+        <is>
+          <t>L726: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O281" s="1" t="inlineStr"/>
+      <c r="P281" s="1" t="inlineStr"/>
+      <c r="Q281" s="1" t="inlineStr"/>
+      <c r="R281" s="1" t="inlineStr"/>
+      <c r="S281" s="1" t="inlineStr"/>
+      <c r="T281" s="1" t="inlineStr"/>
+      <c r="U281" s="1" t="inlineStr"/>
+      <c r="V281" s="1" t="inlineStr"/>
+      <c r="W281" s="1" t="inlineStr"/>
+      <c r="X281" s="1" t="inlineStr"/>
+      <c r="Y281" s="1" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr"/>
+      <c r="B282" s="1" t="inlineStr"/>
+      <c r="C282" s="1" t="inlineStr"/>
+      <c r="D282" s="1" t="inlineStr"/>
+      <c r="E282" s="1" t="inlineStr"/>
+      <c r="F282" s="1" t="inlineStr"/>
+      <c r="G282" s="1" t="inlineStr"/>
+      <c r="H282" s="1" t="inlineStr"/>
+      <c r="I282" s="1" t="inlineStr"/>
+      <c r="J282" s="1" t="inlineStr"/>
+      <c r="K282" s="1" t="inlineStr"/>
+      <c r="L282" s="1" t="inlineStr"/>
+      <c r="M282" s="1" t="inlineStr"/>
+      <c r="N282" s="1" t="inlineStr">
+        <is>
+          <t>L727: isolated marker/symbol line :: 0.</t>
+        </is>
+      </c>
+      <c r="O282" s="1" t="inlineStr"/>
+      <c r="P282" s="1" t="inlineStr"/>
+      <c r="Q282" s="1" t="inlineStr"/>
+      <c r="R282" s="1" t="inlineStr"/>
+      <c r="S282" s="1" t="inlineStr"/>
+      <c r="T282" s="1" t="inlineStr"/>
+      <c r="U282" s="1" t="inlineStr"/>
+      <c r="V282" s="1" t="inlineStr"/>
+      <c r="W282" s="1" t="inlineStr"/>
+      <c r="X282" s="1" t="inlineStr"/>
+      <c r="Y282" s="1" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr"/>
+      <c r="B283" s="1" t="inlineStr"/>
+      <c r="C283" s="1" t="inlineStr"/>
+      <c r="D283" s="1" t="inlineStr"/>
+      <c r="E283" s="1" t="inlineStr"/>
+      <c r="F283" s="1" t="inlineStr"/>
+      <c r="G283" s="1" t="inlineStr"/>
+      <c r="H283" s="1" t="inlineStr"/>
+      <c r="I283" s="1" t="inlineStr"/>
+      <c r="J283" s="1" t="inlineStr"/>
+      <c r="K283" s="1" t="inlineStr"/>
+      <c r="L283" s="1" t="inlineStr"/>
+      <c r="M283" s="1" t="inlineStr"/>
+      <c r="N283" s="1" t="inlineStr">
+        <is>
+          <t>L728: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O283" s="1" t="inlineStr"/>
+      <c r="P283" s="1" t="inlineStr"/>
+      <c r="Q283" s="1" t="inlineStr"/>
+      <c r="R283" s="1" t="inlineStr"/>
+      <c r="S283" s="1" t="inlineStr"/>
+      <c r="T283" s="1" t="inlineStr"/>
+      <c r="U283" s="1" t="inlineStr"/>
+      <c r="V283" s="1" t="inlineStr"/>
+      <c r="W283" s="1" t="inlineStr"/>
+      <c r="X283" s="1" t="inlineStr"/>
+      <c r="Y283" s="1" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr"/>
+      <c r="B284" s="1" t="inlineStr"/>
+      <c r="C284" s="1" t="inlineStr"/>
+      <c r="D284" s="1" t="inlineStr"/>
+      <c r="E284" s="1" t="inlineStr"/>
+      <c r="F284" s="1" t="inlineStr"/>
+      <c r="G284" s="1" t="inlineStr"/>
+      <c r="H284" s="1" t="inlineStr"/>
+      <c r="I284" s="1" t="inlineStr"/>
+      <c r="J284" s="1" t="inlineStr"/>
+      <c r="K284" s="1" t="inlineStr"/>
+      <c r="L284" s="1" t="inlineStr"/>
+      <c r="M284" s="1" t="inlineStr"/>
+      <c r="N284" s="1" t="inlineStr">
+        <is>
+          <t>L729: isolated marker/symbol line :: 276</t>
+        </is>
+      </c>
+      <c r="O284" s="1" t="inlineStr"/>
+      <c r="P284" s="1" t="inlineStr"/>
+      <c r="Q284" s="1" t="inlineStr"/>
+      <c r="R284" s="1" t="inlineStr"/>
+      <c r="S284" s="1" t="inlineStr"/>
+      <c r="T284" s="1" t="inlineStr"/>
+      <c r="U284" s="1" t="inlineStr"/>
+      <c r="V284" s="1" t="inlineStr"/>
+      <c r="W284" s="1" t="inlineStr"/>
+      <c r="X284" s="1" t="inlineStr"/>
+      <c r="Y284" s="1" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr"/>
+      <c r="B285" s="1" t="inlineStr"/>
+      <c r="C285" s="1" t="inlineStr"/>
+      <c r="D285" s="1" t="inlineStr"/>
+      <c r="E285" s="1" t="inlineStr"/>
+      <c r="F285" s="1" t="inlineStr"/>
+      <c r="G285" s="1" t="inlineStr"/>
+      <c r="H285" s="1" t="inlineStr"/>
+      <c r="I285" s="1" t="inlineStr"/>
+      <c r="J285" s="1" t="inlineStr"/>
+      <c r="K285" s="1" t="inlineStr"/>
+      <c r="L285" s="1" t="inlineStr"/>
+      <c r="M285" s="1" t="inlineStr"/>
+      <c r="N285" s="1" t="inlineStr">
+        <is>
+          <t>L730: isolated marker/symbol line :: 376</t>
+        </is>
+      </c>
+      <c r="O285" s="1" t="inlineStr"/>
+      <c r="P285" s="1" t="inlineStr"/>
+      <c r="Q285" s="1" t="inlineStr"/>
+      <c r="R285" s="1" t="inlineStr"/>
+      <c r="S285" s="1" t="inlineStr"/>
+      <c r="T285" s="1" t="inlineStr"/>
+      <c r="U285" s="1" t="inlineStr"/>
+      <c r="V285" s="1" t="inlineStr"/>
+      <c r="W285" s="1" t="inlineStr"/>
+      <c r="X285" s="1" t="inlineStr"/>
+      <c r="Y285" s="1" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr"/>
+      <c r="B286" s="1" t="inlineStr"/>
+      <c r="C286" s="1" t="inlineStr"/>
+      <c r="D286" s="1" t="inlineStr"/>
+      <c r="E286" s="1" t="inlineStr"/>
+      <c r="F286" s="1" t="inlineStr"/>
+      <c r="G286" s="1" t="inlineStr"/>
+      <c r="H286" s="1" t="inlineStr"/>
+      <c r="I286" s="1" t="inlineStr"/>
+      <c r="J286" s="1" t="inlineStr"/>
+      <c r="K286" s="1" t="inlineStr"/>
+      <c r="L286" s="1" t="inlineStr"/>
+      <c r="M286" s="1" t="inlineStr"/>
+      <c r="N286" s="1" t="inlineStr">
+        <is>
+          <t>L731: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
+      <c r="O286" s="1" t="inlineStr"/>
+      <c r="P286" s="1" t="inlineStr"/>
+      <c r="Q286" s="1" t="inlineStr"/>
+      <c r="R286" s="1" t="inlineStr"/>
+      <c r="S286" s="1" t="inlineStr"/>
+      <c r="T286" s="1" t="inlineStr"/>
+      <c r="U286" s="1" t="inlineStr"/>
+      <c r="V286" s="1" t="inlineStr"/>
+      <c r="W286" s="1" t="inlineStr"/>
+      <c r="X286" s="1" t="inlineStr"/>
+      <c r="Y286" s="1" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr"/>
+      <c r="B287" s="1" t="inlineStr"/>
+      <c r="C287" s="1" t="inlineStr"/>
+      <c r="D287" s="1" t="inlineStr"/>
+      <c r="E287" s="1" t="inlineStr"/>
+      <c r="F287" s="1" t="inlineStr"/>
+      <c r="G287" s="1" t="inlineStr"/>
+      <c r="H287" s="1" t="inlineStr"/>
+      <c r="I287" s="1" t="inlineStr"/>
+      <c r="J287" s="1" t="inlineStr"/>
+      <c r="K287" s="1" t="inlineStr"/>
+      <c r="L287" s="1" t="inlineStr"/>
+      <c r="M287" s="1" t="inlineStr"/>
+      <c r="N287" s="1" t="inlineStr">
+        <is>
+          <t>L732: isolated marker/symbol line :: R</t>
+        </is>
+      </c>
+      <c r="O287" s="1" t="inlineStr"/>
+      <c r="P287" s="1" t="inlineStr"/>
+      <c r="Q287" s="1" t="inlineStr"/>
+      <c r="R287" s="1" t="inlineStr"/>
+      <c r="S287" s="1" t="inlineStr"/>
+      <c r="T287" s="1" t="inlineStr"/>
+      <c r="U287" s="1" t="inlineStr"/>
+      <c r="V287" s="1" t="inlineStr"/>
+      <c r="W287" s="1" t="inlineStr"/>
+      <c r="X287" s="1" t="inlineStr"/>
+      <c r="Y287" s="1" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr"/>
+      <c r="B288" s="1" t="inlineStr"/>
+      <c r="C288" s="1" t="inlineStr"/>
+      <c r="D288" s="1" t="inlineStr"/>
+      <c r="E288" s="1" t="inlineStr"/>
+      <c r="F288" s="1" t="inlineStr"/>
+      <c r="G288" s="1" t="inlineStr"/>
+      <c r="H288" s="1" t="inlineStr"/>
+      <c r="I288" s="1" t="inlineStr"/>
+      <c r="J288" s="1" t="inlineStr"/>
+      <c r="K288" s="1" t="inlineStr"/>
+      <c r="L288" s="1" t="inlineStr"/>
+      <c r="M288" s="1" t="inlineStr"/>
+      <c r="N288" s="1" t="inlineStr">
+        <is>
+          <t>L733: symbol-only separator/garbage line :: … 1, 551</t>
+        </is>
+      </c>
+      <c r="O288" s="1" t="inlineStr"/>
+      <c r="P288" s="1" t="inlineStr"/>
+      <c r="Q288" s="1" t="inlineStr"/>
+      <c r="R288" s="1" t="inlineStr"/>
+      <c r="S288" s="1" t="inlineStr"/>
+      <c r="T288" s="1" t="inlineStr"/>
+      <c r="U288" s="1" t="inlineStr"/>
+      <c r="V288" s="1" t="inlineStr"/>
+      <c r="W288" s="1" t="inlineStr"/>
+      <c r="X288" s="1" t="inlineStr"/>
+      <c r="Y288" s="1" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr"/>
+      <c r="B289" s="1" t="inlineStr"/>
+      <c r="C289" s="1" t="inlineStr"/>
+      <c r="D289" s="1" t="inlineStr"/>
+      <c r="E289" s="1" t="inlineStr"/>
+      <c r="F289" s="1" t="inlineStr"/>
+      <c r="G289" s="1" t="inlineStr"/>
+      <c r="H289" s="1" t="inlineStr"/>
+      <c r="I289" s="1" t="inlineStr"/>
+      <c r="J289" s="1" t="inlineStr"/>
+      <c r="K289" s="1" t="inlineStr"/>
+      <c r="L289" s="1" t="inlineStr"/>
+      <c r="M289" s="1" t="inlineStr"/>
+      <c r="N289" s="1" t="inlineStr">
+        <is>
+          <t>L734: symbol-only separator/garbage line :: 1, 250</t>
+        </is>
+      </c>
+      <c r="O289" s="1" t="inlineStr"/>
+      <c r="P289" s="1" t="inlineStr"/>
+      <c r="Q289" s="1" t="inlineStr"/>
+      <c r="R289" s="1" t="inlineStr"/>
+      <c r="S289" s="1" t="inlineStr"/>
+      <c r="T289" s="1" t="inlineStr"/>
+      <c r="U289" s="1" t="inlineStr"/>
+      <c r="V289" s="1" t="inlineStr"/>
+      <c r="W289" s="1" t="inlineStr"/>
+      <c r="X289" s="1" t="inlineStr"/>
+      <c r="Y289" s="1" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr"/>
+      <c r="B290" s="1" t="inlineStr"/>
+      <c r="C290" s="1" t="inlineStr"/>
+      <c r="D290" s="1" t="inlineStr"/>
+      <c r="E290" s="1" t="inlineStr"/>
+      <c r="F290" s="1" t="inlineStr"/>
+      <c r="G290" s="1" t="inlineStr"/>
+      <c r="H290" s="1" t="inlineStr"/>
+      <c r="I290" s="1" t="inlineStr"/>
+      <c r="J290" s="1" t="inlineStr"/>
+      <c r="K290" s="1" t="inlineStr"/>
+      <c r="L290" s="1" t="inlineStr"/>
+      <c r="M290" s="1" t="inlineStr"/>
+      <c r="N290" s="1" t="inlineStr">
+        <is>
+          <t>L736: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O290" s="1" t="inlineStr"/>
+      <c r="P290" s="1" t="inlineStr"/>
+      <c r="Q290" s="1" t="inlineStr"/>
+      <c r="R290" s="1" t="inlineStr"/>
+      <c r="S290" s="1" t="inlineStr"/>
+      <c r="T290" s="1" t="inlineStr"/>
+      <c r="U290" s="1" t="inlineStr"/>
+      <c r="V290" s="1" t="inlineStr"/>
+      <c r="W290" s="1" t="inlineStr"/>
+      <c r="X290" s="1" t="inlineStr"/>
+      <c r="Y290" s="1" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr"/>
+      <c r="B291" s="1" t="inlineStr"/>
+      <c r="C291" s="1" t="inlineStr"/>
+      <c r="D291" s="1" t="inlineStr"/>
+      <c r="E291" s="1" t="inlineStr"/>
+      <c r="F291" s="1" t="inlineStr"/>
+      <c r="G291" s="1" t="inlineStr"/>
+      <c r="H291" s="1" t="inlineStr"/>
+      <c r="I291" s="1" t="inlineStr"/>
+      <c r="J291" s="1" t="inlineStr"/>
+      <c r="K291" s="1" t="inlineStr"/>
+      <c r="L291" s="1" t="inlineStr"/>
+      <c r="M291" s="1" t="inlineStr"/>
+      <c r="N291" s="1" t="inlineStr">
+        <is>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O291" s="1" t="inlineStr"/>
+      <c r="P291" s="1" t="inlineStr"/>
+      <c r="Q291" s="1" t="inlineStr"/>
+      <c r="R291" s="1" t="inlineStr"/>
+      <c r="S291" s="1" t="inlineStr"/>
+      <c r="T291" s="1" t="inlineStr"/>
+      <c r="U291" s="1" t="inlineStr"/>
+      <c r="V291" s="1" t="inlineStr"/>
+      <c r="W291" s="1" t="inlineStr"/>
+      <c r="X291" s="1" t="inlineStr"/>
+      <c r="Y291" s="1" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr"/>
+      <c r="B292" s="1" t="inlineStr"/>
+      <c r="C292" s="1" t="inlineStr"/>
+      <c r="D292" s="1" t="inlineStr"/>
+      <c r="E292" s="1" t="inlineStr"/>
+      <c r="F292" s="1" t="inlineStr"/>
+      <c r="G292" s="1" t="inlineStr"/>
+      <c r="H292" s="1" t="inlineStr"/>
+      <c r="I292" s="1" t="inlineStr"/>
+      <c r="J292" s="1" t="inlineStr"/>
+      <c r="K292" s="1" t="inlineStr"/>
+      <c r="L292" s="1" t="inlineStr"/>
+      <c r="M292" s="1" t="inlineStr"/>
+      <c r="N292" s="1" t="inlineStr">
+        <is>
+          <t>L738: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O292" s="1" t="inlineStr"/>
+      <c r="P292" s="1" t="inlineStr"/>
+      <c r="Q292" s="1" t="inlineStr"/>
+      <c r="R292" s="1" t="inlineStr"/>
+      <c r="S292" s="1" t="inlineStr"/>
+      <c r="T292" s="1" t="inlineStr"/>
+      <c r="U292" s="1" t="inlineStr"/>
+      <c r="V292" s="1" t="inlineStr"/>
+      <c r="W292" s="1" t="inlineStr"/>
+      <c r="X292" s="1" t="inlineStr"/>
+      <c r="Y292" s="1" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr"/>
+      <c r="B293" s="1" t="inlineStr"/>
+      <c r="C293" s="1" t="inlineStr"/>
+      <c r="D293" s="1" t="inlineStr"/>
+      <c r="E293" s="1" t="inlineStr"/>
+      <c r="F293" s="1" t="inlineStr"/>
+      <c r="G293" s="1" t="inlineStr"/>
+      <c r="H293" s="1" t="inlineStr"/>
+      <c r="I293" s="1" t="inlineStr"/>
+      <c r="J293" s="1" t="inlineStr"/>
+      <c r="K293" s="1" t="inlineStr"/>
+      <c r="L293" s="1" t="inlineStr"/>
+      <c r="M293" s="1" t="inlineStr"/>
+      <c r="N293" s="1" t="inlineStr">
+        <is>
+          <t>L739: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O293" s="1" t="inlineStr"/>
+      <c r="P293" s="1" t="inlineStr"/>
+      <c r="Q293" s="1" t="inlineStr"/>
+      <c r="R293" s="1" t="inlineStr"/>
+      <c r="S293" s="1" t="inlineStr"/>
+      <c r="T293" s="1" t="inlineStr"/>
+      <c r="U293" s="1" t="inlineStr"/>
+      <c r="V293" s="1" t="inlineStr"/>
+      <c r="W293" s="1" t="inlineStr"/>
+      <c r="X293" s="1" t="inlineStr"/>
+      <c r="Y293" s="1" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr"/>
+      <c r="B294" s="1" t="inlineStr"/>
+      <c r="C294" s="1" t="inlineStr"/>
+      <c r="D294" s="1" t="inlineStr"/>
+      <c r="E294" s="1" t="inlineStr"/>
+      <c r="F294" s="1" t="inlineStr"/>
+      <c r="G294" s="1" t="inlineStr"/>
+      <c r="H294" s="1" t="inlineStr"/>
+      <c r="I294" s="1" t="inlineStr"/>
+      <c r="J294" s="1" t="inlineStr"/>
+      <c r="K294" s="1" t="inlineStr"/>
+      <c r="L294" s="1" t="inlineStr"/>
+      <c r="M294" s="1" t="inlineStr"/>
+      <c r="N294" s="1" t="inlineStr">
+        <is>
+          <t>L740: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O294" s="1" t="inlineStr"/>
+      <c r="P294" s="1" t="inlineStr"/>
+      <c r="Q294" s="1" t="inlineStr"/>
+      <c r="R294" s="1" t="inlineStr"/>
+      <c r="S294" s="1" t="inlineStr"/>
+      <c r="T294" s="1" t="inlineStr"/>
+      <c r="U294" s="1" t="inlineStr"/>
+      <c r="V294" s="1" t="inlineStr"/>
+      <c r="W294" s="1" t="inlineStr"/>
+      <c r="X294" s="1" t="inlineStr"/>
+      <c r="Y294" s="1" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr"/>
+      <c r="B295" s="1" t="inlineStr"/>
+      <c r="C295" s="1" t="inlineStr"/>
+      <c r="D295" s="1" t="inlineStr"/>
+      <c r="E295" s="1" t="inlineStr"/>
+      <c r="F295" s="1" t="inlineStr"/>
+      <c r="G295" s="1" t="inlineStr"/>
+      <c r="H295" s="1" t="inlineStr"/>
+      <c r="I295" s="1" t="inlineStr"/>
+      <c r="J295" s="1" t="inlineStr"/>
+      <c r="K295" s="1" t="inlineStr"/>
+      <c r="L295" s="1" t="inlineStr"/>
+      <c r="M295" s="1" t="inlineStr"/>
+      <c r="N295" s="1" t="inlineStr">
+        <is>
+          <t>L741: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O295" s="1" t="inlineStr"/>
+      <c r="P295" s="1" t="inlineStr"/>
+      <c r="Q295" s="1" t="inlineStr"/>
+      <c r="R295" s="1" t="inlineStr"/>
+      <c r="S295" s="1" t="inlineStr"/>
+      <c r="T295" s="1" t="inlineStr"/>
+      <c r="U295" s="1" t="inlineStr"/>
+      <c r="V295" s="1" t="inlineStr"/>
+      <c r="W295" s="1" t="inlineStr"/>
+      <c r="X295" s="1" t="inlineStr"/>
+      <c r="Y295" s="1" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr"/>
+      <c r="B296" s="1" t="inlineStr"/>
+      <c r="C296" s="1" t="inlineStr"/>
+      <c r="D296" s="1" t="inlineStr"/>
+      <c r="E296" s="1" t="inlineStr"/>
+      <c r="F296" s="1" t="inlineStr"/>
+      <c r="G296" s="1" t="inlineStr"/>
+      <c r="H296" s="1" t="inlineStr"/>
+      <c r="I296" s="1" t="inlineStr"/>
+      <c r="J296" s="1" t="inlineStr"/>
+      <c r="K296" s="1" t="inlineStr"/>
+      <c r="L296" s="1" t="inlineStr"/>
+      <c r="M296" s="1" t="inlineStr"/>
+      <c r="N296" s="1" t="inlineStr">
+        <is>
+          <t>L742: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+        </is>
+      </c>
+      <c r="O296" s="1" t="inlineStr"/>
+      <c r="P296" s="1" t="inlineStr"/>
+      <c r="Q296" s="1" t="inlineStr"/>
+      <c r="R296" s="1" t="inlineStr"/>
+      <c r="S296" s="1" t="inlineStr"/>
+      <c r="T296" s="1" t="inlineStr"/>
+      <c r="U296" s="1" t="inlineStr"/>
+      <c r="V296" s="1" t="inlineStr"/>
+      <c r="W296" s="1" t="inlineStr"/>
+      <c r="X296" s="1" t="inlineStr"/>
+      <c r="Y296" s="1" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr"/>
+      <c r="B297" s="1" t="inlineStr"/>
+      <c r="C297" s="1" t="inlineStr"/>
+      <c r="D297" s="1" t="inlineStr"/>
+      <c r="E297" s="1" t="inlineStr"/>
+      <c r="F297" s="1" t="inlineStr"/>
+      <c r="G297" s="1" t="inlineStr"/>
+      <c r="H297" s="1" t="inlineStr"/>
+      <c r="I297" s="1" t="inlineStr"/>
+      <c r="J297" s="1" t="inlineStr"/>
+      <c r="K297" s="1" t="inlineStr"/>
+      <c r="L297" s="1" t="inlineStr"/>
+      <c r="M297" s="1" t="inlineStr"/>
+      <c r="N297" s="1" t="inlineStr">
+        <is>
+          <t>L745: isolated marker/symbol line :: w</t>
+        </is>
+      </c>
+      <c r="O297" s="1" t="inlineStr"/>
+      <c r="P297" s="1" t="inlineStr"/>
+      <c r="Q297" s="1" t="inlineStr"/>
+      <c r="R297" s="1" t="inlineStr"/>
+      <c r="S297" s="1" t="inlineStr"/>
+      <c r="T297" s="1" t="inlineStr"/>
+      <c r="U297" s="1" t="inlineStr"/>
+      <c r="V297" s="1" t="inlineStr"/>
+      <c r="W297" s="1" t="inlineStr"/>
+      <c r="X297" s="1" t="inlineStr"/>
+      <c r="Y297" s="1" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr"/>
+      <c r="B298" s="1" t="inlineStr"/>
+      <c r="C298" s="1" t="inlineStr"/>
+      <c r="D298" s="1" t="inlineStr"/>
+      <c r="E298" s="1" t="inlineStr"/>
+      <c r="F298" s="1" t="inlineStr"/>
+      <c r="G298" s="1" t="inlineStr"/>
+      <c r="H298" s="1" t="inlineStr"/>
+      <c r="I298" s="1" t="inlineStr"/>
+      <c r="J298" s="1" t="inlineStr"/>
+      <c r="K298" s="1" t="inlineStr"/>
+      <c r="L298" s="1" t="inlineStr"/>
+      <c r="M298" s="1" t="inlineStr"/>
+      <c r="N298" s="1" t="inlineStr">
+        <is>
+          <t>L747: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O298" s="1" t="inlineStr"/>
+      <c r="P298" s="1" t="inlineStr"/>
+      <c r="Q298" s="1" t="inlineStr"/>
+      <c r="R298" s="1" t="inlineStr"/>
+      <c r="S298" s="1" t="inlineStr"/>
+      <c r="T298" s="1" t="inlineStr"/>
+      <c r="U298" s="1" t="inlineStr"/>
+      <c r="V298" s="1" t="inlineStr"/>
+      <c r="W298" s="1" t="inlineStr"/>
+      <c r="X298" s="1" t="inlineStr"/>
+      <c r="Y298" s="1" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr"/>
+      <c r="B299" s="1" t="inlineStr"/>
+      <c r="C299" s="1" t="inlineStr"/>
+      <c r="D299" s="1" t="inlineStr"/>
+      <c r="E299" s="1" t="inlineStr"/>
+      <c r="F299" s="1" t="inlineStr"/>
+      <c r="G299" s="1" t="inlineStr"/>
+      <c r="H299" s="1" t="inlineStr"/>
+      <c r="I299" s="1" t="inlineStr"/>
+      <c r="J299" s="1" t="inlineStr"/>
+      <c r="K299" s="1" t="inlineStr"/>
+      <c r="L299" s="1" t="inlineStr"/>
+      <c r="M299" s="1" t="inlineStr"/>
+      <c r="N299" s="1" t="inlineStr">
+        <is>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O299" s="1" t="inlineStr"/>
+      <c r="P299" s="1" t="inlineStr"/>
+      <c r="Q299" s="1" t="inlineStr"/>
+      <c r="R299" s="1" t="inlineStr"/>
+      <c r="S299" s="1" t="inlineStr"/>
+      <c r="T299" s="1" t="inlineStr"/>
+      <c r="U299" s="1" t="inlineStr"/>
+      <c r="V299" s="1" t="inlineStr"/>
+      <c r="W299" s="1" t="inlineStr"/>
+      <c r="X299" s="1" t="inlineStr"/>
+      <c r="Y299" s="1" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr"/>
+      <c r="B300" s="1" t="inlineStr"/>
+      <c r="C300" s="1" t="inlineStr"/>
+      <c r="D300" s="1" t="inlineStr"/>
+      <c r="E300" s="1" t="inlineStr"/>
+      <c r="F300" s="1" t="inlineStr"/>
+      <c r="G300" s="1" t="inlineStr"/>
+      <c r="H300" s="1" t="inlineStr"/>
+      <c r="I300" s="1" t="inlineStr"/>
+      <c r="J300" s="1" t="inlineStr"/>
+      <c r="K300" s="1" t="inlineStr"/>
+      <c r="L300" s="1" t="inlineStr"/>
+      <c r="M300" s="1" t="inlineStr"/>
+      <c r="N300" s="1" t="inlineStr">
+        <is>
+          <t>L849: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O300" s="1" t="inlineStr"/>
+      <c r="P300" s="1" t="inlineStr"/>
+      <c r="Q300" s="1" t="inlineStr"/>
+      <c r="R300" s="1" t="inlineStr"/>
+      <c r="S300" s="1" t="inlineStr"/>
+      <c r="T300" s="1" t="inlineStr"/>
+      <c r="U300" s="1" t="inlineStr"/>
+      <c r="V300" s="1" t="inlineStr"/>
+      <c r="W300" s="1" t="inlineStr"/>
+      <c r="X300" s="1" t="inlineStr"/>
+      <c r="Y300" s="1" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr"/>
+      <c r="B301" s="1" t="inlineStr"/>
+      <c r="C301" s="1" t="inlineStr"/>
+      <c r="D301" s="1" t="inlineStr"/>
+      <c r="E301" s="1" t="inlineStr"/>
+      <c r="F301" s="1" t="inlineStr"/>
+      <c r="G301" s="1" t="inlineStr"/>
+      <c r="H301" s="1" t="inlineStr"/>
+      <c r="I301" s="1" t="inlineStr"/>
+      <c r="J301" s="1" t="inlineStr"/>
+      <c r="K301" s="1" t="inlineStr"/>
+      <c r="L301" s="1" t="inlineStr"/>
+      <c r="M301" s="1" t="inlineStr"/>
+      <c r="N301" s="1" t="inlineStr">
+        <is>
+          <t>L967: isolated marker/symbol line :: 18</t>
+        </is>
+      </c>
+      <c r="O301" s="1" t="inlineStr"/>
+      <c r="P301" s="1" t="inlineStr"/>
+      <c r="Q301" s="1" t="inlineStr"/>
+      <c r="R301" s="1" t="inlineStr"/>
+      <c r="S301" s="1" t="inlineStr"/>
+      <c r="T301" s="1" t="inlineStr"/>
+      <c r="U301" s="1" t="inlineStr"/>
+      <c r="V301" s="1" t="inlineStr"/>
+      <c r="W301" s="1" t="inlineStr"/>
+      <c r="X301" s="1" t="inlineStr"/>
+      <c r="Y301" s="1" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr"/>
+      <c r="B302" s="1" t="inlineStr"/>
+      <c r="C302" s="1" t="inlineStr"/>
+      <c r="D302" s="1" t="inlineStr"/>
+      <c r="E302" s="1" t="inlineStr"/>
+      <c r="F302" s="1" t="inlineStr"/>
+      <c r="G302" s="1" t="inlineStr"/>
+      <c r="H302" s="1" t="inlineStr"/>
+      <c r="I302" s="1" t="inlineStr"/>
+      <c r="J302" s="1" t="inlineStr"/>
+      <c r="K302" s="1" t="inlineStr"/>
+      <c r="L302" s="1" t="inlineStr"/>
+      <c r="M302" s="1" t="inlineStr"/>
+      <c r="N302" s="1" t="inlineStr">
+        <is>
+          <t>L969: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
+      <c r="O302" s="1" t="inlineStr"/>
+      <c r="P302" s="1" t="inlineStr"/>
+      <c r="Q302" s="1" t="inlineStr"/>
+      <c r="R302" s="1" t="inlineStr"/>
+      <c r="S302" s="1" t="inlineStr"/>
+      <c r="T302" s="1" t="inlineStr"/>
+      <c r="U302" s="1" t="inlineStr"/>
+      <c r="V302" s="1" t="inlineStr"/>
+      <c r="W302" s="1" t="inlineStr"/>
+      <c r="X302" s="1" t="inlineStr"/>
+      <c r="Y302" s="1" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr"/>
+      <c r="B303" s="1" t="inlineStr"/>
+      <c r="C303" s="1" t="inlineStr"/>
+      <c r="D303" s="1" t="inlineStr"/>
+      <c r="E303" s="1" t="inlineStr"/>
+      <c r="F303" s="1" t="inlineStr"/>
+      <c r="G303" s="1" t="inlineStr"/>
+      <c r="H303" s="1" t="inlineStr"/>
+      <c r="I303" s="1" t="inlineStr"/>
+      <c r="J303" s="1" t="inlineStr"/>
+      <c r="K303" s="1" t="inlineStr"/>
+      <c r="L303" s="1" t="inlineStr"/>
+      <c r="M303" s="1" t="inlineStr"/>
+      <c r="N303" s="1" t="inlineStr">
+        <is>
+          <t>L991: symbol-only separator/garbage line :: $5.25</t>
+        </is>
+      </c>
+      <c r="O303" s="1" t="inlineStr"/>
+      <c r="P303" s="1" t="inlineStr"/>
+      <c r="Q303" s="1" t="inlineStr"/>
+      <c r="R303" s="1" t="inlineStr"/>
+      <c r="S303" s="1" t="inlineStr"/>
+      <c r="T303" s="1" t="inlineStr"/>
+      <c r="U303" s="1" t="inlineStr"/>
+      <c r="V303" s="1" t="inlineStr"/>
+      <c r="W303" s="1" t="inlineStr"/>
+      <c r="X303" s="1" t="inlineStr"/>
+      <c r="Y303" s="1" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr"/>
+      <c r="B304" s="1" t="inlineStr"/>
+      <c r="C304" s="1" t="inlineStr"/>
+      <c r="D304" s="1" t="inlineStr"/>
+      <c r="E304" s="1" t="inlineStr"/>
+      <c r="F304" s="1" t="inlineStr"/>
+      <c r="G304" s="1" t="inlineStr"/>
+      <c r="H304" s="1" t="inlineStr"/>
+      <c r="I304" s="1" t="inlineStr"/>
+      <c r="J304" s="1" t="inlineStr"/>
+      <c r="K304" s="1" t="inlineStr"/>
+      <c r="L304" s="1" t="inlineStr"/>
+      <c r="M304" s="1" t="inlineStr"/>
+      <c r="N304" s="1" t="inlineStr">
+        <is>
+          <t>L993: isolated marker/symbol line :: c</t>
+        </is>
+      </c>
+      <c r="O304" s="1" t="inlineStr"/>
+      <c r="P304" s="1" t="inlineStr"/>
+      <c r="Q304" s="1" t="inlineStr"/>
+      <c r="R304" s="1" t="inlineStr"/>
+      <c r="S304" s="1" t="inlineStr"/>
+      <c r="T304" s="1" t="inlineStr"/>
+      <c r="U304" s="1" t="inlineStr"/>
+      <c r="V304" s="1" t="inlineStr"/>
+      <c r="W304" s="1" t="inlineStr"/>
+      <c r="X304" s="1" t="inlineStr"/>
+      <c r="Y304" s="1" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr"/>
+      <c r="B305" s="1" t="inlineStr"/>
+      <c r="C305" s="1" t="inlineStr"/>
+      <c r="D305" s="1" t="inlineStr"/>
+      <c r="E305" s="1" t="inlineStr"/>
+      <c r="F305" s="1" t="inlineStr"/>
+      <c r="G305" s="1" t="inlineStr"/>
+      <c r="H305" s="1" t="inlineStr"/>
+      <c r="I305" s="1" t="inlineStr"/>
+      <c r="J305" s="1" t="inlineStr"/>
+      <c r="K305" s="1" t="inlineStr"/>
+      <c r="L305" s="1" t="inlineStr"/>
+      <c r="M305" s="1" t="inlineStr"/>
+      <c r="N305" s="1" t="inlineStr">
+        <is>
+          <t>L1008: isolated marker/symbol line :: d</t>
+        </is>
+      </c>
+      <c r="O305" s="1" t="inlineStr"/>
+      <c r="P305" s="1" t="inlineStr"/>
+      <c r="Q305" s="1" t="inlineStr"/>
+      <c r="R305" s="1" t="inlineStr"/>
+      <c r="S305" s="1" t="inlineStr"/>
+      <c r="T305" s="1" t="inlineStr"/>
+      <c r="U305" s="1" t="inlineStr"/>
+      <c r="V305" s="1" t="inlineStr"/>
+      <c r="W305" s="1" t="inlineStr"/>
+      <c r="X305" s="1" t="inlineStr"/>
+      <c r="Y305" s="1" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr"/>
+      <c r="B306" s="1" t="inlineStr"/>
+      <c r="C306" s="1" t="inlineStr"/>
+      <c r="D306" s="1" t="inlineStr"/>
+      <c r="E306" s="1" t="inlineStr"/>
+      <c r="F306" s="1" t="inlineStr"/>
+      <c r="G306" s="1" t="inlineStr"/>
+      <c r="H306" s="1" t="inlineStr"/>
+      <c r="I306" s="1" t="inlineStr"/>
+      <c r="J306" s="1" t="inlineStr"/>
+      <c r="K306" s="1" t="inlineStr"/>
+      <c r="L306" s="1" t="inlineStr"/>
+      <c r="M306" s="1" t="inlineStr"/>
+      <c r="N306" s="1" t="inlineStr">
+        <is>
+          <t>L1038: symbol-only separator/garbage line :: $1.50.</t>
+        </is>
+      </c>
+      <c r="O306" s="1" t="inlineStr"/>
+      <c r="P306" s="1" t="inlineStr"/>
+      <c r="Q306" s="1" t="inlineStr"/>
+      <c r="R306" s="1" t="inlineStr"/>
+      <c r="S306" s="1" t="inlineStr"/>
+      <c r="T306" s="1" t="inlineStr"/>
+      <c r="U306" s="1" t="inlineStr"/>
+      <c r="V306" s="1" t="inlineStr"/>
+      <c r="W306" s="1" t="inlineStr"/>
+      <c r="X306" s="1" t="inlineStr"/>
+      <c r="Y306" s="1" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr"/>
+      <c r="B307" s="1" t="inlineStr"/>
+      <c r="C307" s="1" t="inlineStr"/>
+      <c r="D307" s="1" t="inlineStr"/>
+      <c r="E307" s="1" t="inlineStr"/>
+      <c r="F307" s="1" t="inlineStr"/>
+      <c r="G307" s="1" t="inlineStr"/>
+      <c r="H307" s="1" t="inlineStr"/>
+      <c r="I307" s="1" t="inlineStr"/>
+      <c r="J307" s="1" t="inlineStr"/>
+      <c r="K307" s="1" t="inlineStr"/>
+      <c r="L307" s="1" t="inlineStr"/>
+      <c r="M307" s="1" t="inlineStr"/>
+      <c r="N307" s="1" t="inlineStr">
+        <is>
+          <t>L1064: isolated marker/symbol line :: 1 「</t>
+        </is>
+      </c>
+      <c r="O307" s="1" t="inlineStr"/>
+      <c r="P307" s="1" t="inlineStr"/>
+      <c r="Q307" s="1" t="inlineStr"/>
+      <c r="R307" s="1" t="inlineStr"/>
+      <c r="S307" s="1" t="inlineStr"/>
+      <c r="T307" s="1" t="inlineStr"/>
+      <c r="U307" s="1" t="inlineStr"/>
+      <c r="V307" s="1" t="inlineStr"/>
+      <c r="W307" s="1" t="inlineStr"/>
+      <c r="X307" s="1" t="inlineStr"/>
+      <c r="Y307" s="1" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr"/>
+      <c r="B308" s="1" t="inlineStr"/>
+      <c r="C308" s="1" t="inlineStr"/>
+      <c r="D308" s="1" t="inlineStr"/>
+      <c r="E308" s="1" t="inlineStr"/>
+      <c r="F308" s="1" t="inlineStr"/>
+      <c r="G308" s="1" t="inlineStr"/>
+      <c r="H308" s="1" t="inlineStr"/>
+      <c r="I308" s="1" t="inlineStr"/>
+      <c r="J308" s="1" t="inlineStr"/>
+      <c r="K308" s="1" t="inlineStr"/>
+      <c r="L308" s="1" t="inlineStr"/>
+      <c r="M308" s="1" t="inlineStr"/>
+      <c r="N308" s="1" t="inlineStr">
+        <is>
+          <t>L1089: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
+      <c r="O308" s="1" t="inlineStr"/>
+      <c r="P308" s="1" t="inlineStr"/>
+      <c r="Q308" s="1" t="inlineStr"/>
+      <c r="R308" s="1" t="inlineStr"/>
+      <c r="S308" s="1" t="inlineStr"/>
+      <c r="T308" s="1" t="inlineStr"/>
+      <c r="U308" s="1" t="inlineStr"/>
+      <c r="V308" s="1" t="inlineStr"/>
+      <c r="W308" s="1" t="inlineStr"/>
+      <c r="X308" s="1" t="inlineStr"/>
+      <c r="Y308" s="1" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr"/>
+      <c r="B309" s="1" t="inlineStr"/>
+      <c r="C309" s="1" t="inlineStr"/>
+      <c r="D309" s="1" t="inlineStr"/>
+      <c r="E309" s="1" t="inlineStr"/>
+      <c r="F309" s="1" t="inlineStr"/>
+      <c r="G309" s="1" t="inlineStr"/>
+      <c r="H309" s="1" t="inlineStr"/>
+      <c r="I309" s="1" t="inlineStr"/>
+      <c r="J309" s="1" t="inlineStr"/>
+      <c r="K309" s="1" t="inlineStr"/>
+      <c r="L309" s="1" t="inlineStr"/>
+      <c r="M309" s="1" t="inlineStr"/>
+      <c r="N309" s="1" t="inlineStr">
+        <is>
+          <t>L1090: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O309" s="1" t="inlineStr"/>
+      <c r="P309" s="1" t="inlineStr"/>
+      <c r="Q309" s="1" t="inlineStr"/>
+      <c r="R309" s="1" t="inlineStr"/>
+      <c r="S309" s="1" t="inlineStr"/>
+      <c r="T309" s="1" t="inlineStr"/>
+      <c r="U309" s="1" t="inlineStr"/>
+      <c r="V309" s="1" t="inlineStr"/>
+      <c r="W309" s="1" t="inlineStr"/>
+      <c r="X309" s="1" t="inlineStr"/>
+      <c r="Y309" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
